--- a/CSO_prediction/constrained_data_driven_prediction/sensitivity_analysis/selecting the best M.xlsx
+++ b/CSO_prediction/constrained_data_driven_prediction/sensitivity_analysis/selecting the best M.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universityofexeteruk-my.sharepoint.com/personal/mr861_exeter_ac_uk/Documents/Desktop/model_Faf/CSO_prediction/constrained_data_driven_prediction/sensitivity_analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="109" documentId="11_F25DC773A252ABDACC10484C319C55345ADE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42B708A8-C6AF-4858-8FF8-DC0348961BA6}"/>
+  <xr:revisionPtr revIDLastSave="152" documentId="11_F25DC773A252ABDACC10484C319C55345ADE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F404CF12-22E0-44FB-B411-BA509434FAF0}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="23">
   <si>
     <t>M</t>
   </si>
@@ -94,6 +94,18 @@
   </si>
   <si>
     <t>length (days)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peak flow error </t>
+  </si>
+  <si>
+    <t>max actual</t>
+  </si>
+  <si>
+    <t>max predicted</t>
+  </si>
+  <si>
+    <t>60-40</t>
   </si>
 </sst>
 </file>
@@ -2860,248 +2872,366 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F7B49CC-5EEC-44E0-BF7E-CD27EE1A1B6D}">
-  <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:J16"/>
+  <sheetFormatPr defaultColWidth="9.23046875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="12.84375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="17.53515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="29.3046875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16.23046875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="9.23046875" style="1"/>
-    <col min="6" max="6" width="12.84375" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.23046875" style="1"/>
+    <col min="2" max="2" width="18.84375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.53515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="29.3046875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.23046875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.23046875" style="1"/>
+    <col min="7" max="7" width="12.84375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9.23046875" style="1"/>
+    <col min="9" max="9" width="19.3046875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="22.69140625" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.23046875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="I1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="1">
+      <c r="C2" s="1">
         <v>46.014099999999999</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="1">
+      <c r="E2" s="1">
         <v>2019</v>
       </c>
-      <c r="E2" s="1">
+      <c r="F2" s="1">
         <v>250</v>
       </c>
-      <c r="F2" s="1">
+      <c r="G2" s="1">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="1">
+      <c r="C3" s="2">
         <v>40.61</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="1">
+      <c r="E3" s="1">
         <v>2019</v>
       </c>
-      <c r="E3" s="1">
+      <c r="F3" s="1">
         <v>250</v>
       </c>
-      <c r="F3" s="1">
+      <c r="G3" s="1">
         <v>30</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="1">
+      <c r="C4" s="1">
         <v>59.394599999999997</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="1">
+      <c r="E4" s="1">
         <v>2019</v>
       </c>
-      <c r="E4" s="1">
+      <c r="F4" s="1">
         <v>250</v>
       </c>
-      <c r="F4" s="1">
+      <c r="G4" s="1">
         <v>30</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="2">
+        <f>100*(I8-J8)/I8</f>
+        <v>49.29253995243478</v>
+      </c>
+      <c r="C8" s="1">
         <v>81.926299999999998</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="1">
+      <c r="E8" s="1">
         <v>2021</v>
       </c>
-      <c r="E8" s="1">
+      <c r="F8" s="1">
         <v>250</v>
       </c>
-      <c r="F8" s="1">
+      <c r="G8" s="1">
         <v>30</v>
       </c>
+      <c r="I8" s="1">
+        <v>939.63610000000006</v>
+      </c>
+      <c r="J8" s="1">
+        <v>476.46559999999999</v>
+      </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="1">
+        <f t="shared" ref="B9:B12" si="0">100*(I9-J9)/I9</f>
+        <v>50.98571670458383</v>
+      </c>
+      <c r="C9" s="2">
         <v>77.024199999999993</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="1">
+      <c r="E9" s="1">
         <v>2021</v>
       </c>
-      <c r="E9" s="1">
+      <c r="F9" s="1">
         <v>250</v>
       </c>
-      <c r="F9" s="1">
+      <c r="G9" s="1">
         <v>30</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="H9" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="I9" s="1">
+        <v>939.63610000000006</v>
+      </c>
+      <c r="J9" s="1">
+        <v>460.55590000000001</v>
+      </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B10" s="1">
+        <f t="shared" si="0"/>
+        <v>50.991729670667191</v>
+      </c>
+      <c r="C10" s="1">
         <v>93.453000000000003</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="1">
+      <c r="E10" s="1">
         <v>2021</v>
       </c>
-      <c r="E10" s="1">
+      <c r="F10" s="1">
         <v>250</v>
       </c>
-      <c r="F10" s="1">
+      <c r="G10" s="1">
         <v>30</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="H10" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="I10" s="1">
+        <v>939.63610000000006</v>
+      </c>
+      <c r="J10" s="1">
+        <v>460.49939999999998</v>
+      </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B11" s="1">
+        <f t="shared" si="0"/>
+        <v>51.320559097293092</v>
+      </c>
+      <c r="C11" s="1">
         <v>80.945099999999996</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="1">
+      <c r="E11" s="1">
         <v>2021</v>
       </c>
-      <c r="E11" s="1">
+      <c r="F11" s="1">
         <v>250</v>
       </c>
-      <c r="F11" s="1">
+      <c r="G11" s="1">
         <v>30</v>
       </c>
+      <c r="I11" s="1">
+        <v>939.63610000000006</v>
+      </c>
+      <c r="J11" s="1">
+        <v>457.40960000000001</v>
+      </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A12" s="2" t="s">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A12" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B12" s="1">
+        <f t="shared" si="0"/>
+        <v>52.490331097325871</v>
+      </c>
+      <c r="C12" s="2">
         <v>74.618799999999993</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="D12" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="1">
+      <c r="E12" s="1">
         <v>2021</v>
       </c>
-      <c r="E12" s="1">
+      <c r="F12" s="1">
         <v>250</v>
       </c>
-      <c r="F12" s="1">
+      <c r="G12" s="1">
         <v>30</v>
       </c>
+      <c r="I12" s="1">
+        <v>939.63610000000006</v>
+      </c>
+      <c r="J12" s="1">
+        <v>446.41800000000001</v>
+      </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B13" s="1">
+        <f>100*(I13-J13)/I13</f>
+        <v>51.082477567645604</v>
+      </c>
+      <c r="C13" s="1">
         <v>84.975499999999997</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="1">
+      <c r="E13" s="1">
         <v>2021</v>
       </c>
-      <c r="E13" s="1">
+      <c r="F13" s="1">
         <v>250</v>
       </c>
-      <c r="F13" s="1">
+      <c r="G13" s="1">
         <v>30</v>
+      </c>
+      <c r="I13" s="1">
+        <v>939.63610000000006</v>
+      </c>
+      <c r="J13" s="1">
+        <v>459.64670000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="1">
+        <f>100*(I14-J14)/I14</f>
+        <v>50.770292882531869</v>
+      </c>
+      <c r="C14" s="1">
+        <v>89.19</v>
+      </c>
+      <c r="I14" s="1">
+        <v>939.63610000000006</v>
+      </c>
+      <c r="J14" s="1">
+        <v>462.58010000000002</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="1">
+        <f t="shared" ref="B15:B16" si="1">100*(I16-J16)/I16</f>
+        <v>40.98462159978741</v>
+      </c>
+      <c r="E16" s="1">
+        <v>2021</v>
+      </c>
+      <c r="F16" s="1">
+        <v>250</v>
+      </c>
+      <c r="G16" s="1">
+        <v>90</v>
+      </c>
+      <c r="I16" s="1">
+        <v>939.63610000000006</v>
+      </c>
+      <c r="J16" s="1">
+        <v>554.52980000000002</v>
       </c>
     </row>
   </sheetData>
